--- a/public_html/data/excel/ingreso_mensual/PagosRecibidos_31624_NUTRICION_2024-11-09.xlsx
+++ b/public_html/data/excel/ingreso_mensual/PagosRecibidos_31624_NUTRICION_2024-11-09.xlsx
@@ -691,7 +691,7 @@
         <v>148.0</v>
       </c>
       <c r="H5" s="5">
-        <v>12218.4</v>
+        <v>12480.4</v>
       </c>
       <c r="I5" s="1">
         <v>1075.8965517241</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>1213.15</v>
+        <v>1457.35</v>
       </c>
       <c r="I9" s="1">
         <v>125.63362068966</v>
@@ -926,7 +926,7 @@
         <v>80.0</v>
       </c>
       <c r="H10" s="5">
-        <v>15838.3</v>
+        <v>16060.8</v>
       </c>
       <c r="I10" s="1">
         <v>1384.5517241379</v>
@@ -973,7 +973,7 @@
         <v>41.0</v>
       </c>
       <c r="H11" s="5">
-        <v>4564.1</v>
+        <v>4523.1</v>
       </c>
       <c r="I11" s="1">
         <v>389.9224137931</v>
